--- a/src/resources/data/CourseFilter.xlsx
+++ b/src/resources/data/CourseFilter.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4330" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Levels" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterate="1" iterateCount="1000" iterateDelta="0.01"/>
 </workbook>
@@ -424,6 +424,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">

--- a/src/resources/data/CourseFilter.xlsx
+++ b/src/resources/data/CourseFilter.xlsx
@@ -1,18 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Team5_playwright\BDD_Playwright_Automation_Project\src\resources\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4330" tabRatio="500"/>
+    <workbookView tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Levels" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" name="Levels" sheetId="1"/>
   </sheets>
   <calcPr calcId="0" iterate="1" iterateCount="1000" iterateDelta="0.01"/>
 </workbook>
@@ -42,18 +36,26 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="11"/>
+      <color auto="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="11"/>
+      <color auto="1"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -65,14 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -81,35 +76,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1">
-      <alignment vertical="top"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -421,44 +411,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{EFE3CCA2-BAD2-4A13-8EC9-6EF6C46963E0}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="1" max="1" width="12.57421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" customHeight="1">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" customHeight="1">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" customHeight="1">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst/>
 </worksheet>
 </file>